--- a/financas.xlsx
+++ b/financas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fea781441e4f247c/Documentos/Finanças/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D7C9464-DE5D-46C5-BCE6-1C2D5AC1D4B3}"/>
+  <xr:revisionPtr revIDLastSave="362" documentId="8_{B7224BD9-7546-4D39-AD24-E9DCD61BD67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78543C44-ABD6-4823-8F6D-B177A98B3AB2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Itaú!$C$4:$Q$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NuBank!$C$5:$Q$150</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="234">
   <si>
     <t>Valor para o mês</t>
   </si>
@@ -375,6 +375,54 @@
     <t>Pontual</t>
   </si>
   <si>
+    <t>Psicóloga</t>
+  </si>
+  <si>
+    <t>pontual</t>
+  </si>
+  <si>
+    <t>Bonfas Chope</t>
+  </si>
+  <si>
+    <t>Cm</t>
+  </si>
+  <si>
+    <t>Bonfas Lanche</t>
+  </si>
+  <si>
+    <t>Remédios Stella</t>
+  </si>
+  <si>
+    <t>Ração Brida</t>
+  </si>
+  <si>
+    <t>Pagamento Ração Brida</t>
+  </si>
+  <si>
+    <t>TENTAR ADIATNAR</t>
+  </si>
+  <si>
+    <t>Moletom Brutal Kill</t>
+  </si>
+  <si>
+    <t>Uber Mr. Jones</t>
+  </si>
+  <si>
+    <t>Gibs</t>
+  </si>
+  <si>
+    <t>Serviço de nuvem da câmera</t>
+  </si>
+  <si>
+    <t>Gasolina</t>
+  </si>
+  <si>
+    <t>Rappi</t>
+  </si>
+  <si>
+    <t>Lanche</t>
+  </si>
+  <si>
     <t>Vivo</t>
   </si>
   <si>
@@ -405,313 +453,301 @@
     <t>Movimentação</t>
   </si>
   <si>
+    <t>Adiantamento Salário</t>
+  </si>
+  <si>
+    <t>Seguro</t>
+  </si>
+  <si>
+    <t>Reembolso Psicóloga</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Com turbo</t>
+  </si>
+  <si>
+    <t>Caixinha Guilherme</t>
+  </si>
+  <si>
+    <t>Caixinha Stella</t>
+  </si>
+  <si>
+    <t>Detran</t>
+  </si>
+  <si>
+    <t>Sem turbo</t>
+  </si>
+  <si>
+    <t>IPVAs + Licenciamento</t>
+  </si>
+  <si>
+    <t>Tirando da Caixinha Turbo</t>
+  </si>
+  <si>
+    <t>Adiantamento Stella Janeiro</t>
+  </si>
+  <si>
+    <t>Ajuste NuConta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cidadania+Veterinário Brida </t>
+  </si>
+  <si>
+    <t>Devolução Stella</t>
+  </si>
+  <si>
+    <t>Salário afastamento</t>
+  </si>
+  <si>
+    <t>Emergência Geleia+Vurtuoso+Terra Brasa</t>
+  </si>
+  <si>
+    <t>Adiantamento Stella</t>
+  </si>
+  <si>
+    <t>Galpãozin</t>
+  </si>
+  <si>
+    <t>Fisioterapia Stella</t>
+  </si>
+  <si>
+    <t>Pagamento Fasolina + Almoço Shirley + Linkedin+Bonfas</t>
+  </si>
+  <si>
+    <t>INSS</t>
+  </si>
+  <si>
+    <t>Pagamento Superbowl</t>
+  </si>
+  <si>
+    <t>SiSenor</t>
+  </si>
+  <si>
+    <t>Alemão</t>
+  </si>
+  <si>
+    <t>Portão</t>
+  </si>
+  <si>
+    <t>Devolução  Stella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonfa's </t>
+  </si>
+  <si>
+    <t>Ilumeo Março - WillBank</t>
+  </si>
+  <si>
+    <t>Remédio e Consulta Stella</t>
+  </si>
+  <si>
+    <t>Pagamentos</t>
+  </si>
+  <si>
+    <t>Adiantamento INSS</t>
+  </si>
+  <si>
+    <t>Adicional</t>
+  </si>
+  <si>
+    <t>Pagamentos fds Páscoa</t>
+  </si>
+  <si>
+    <t>Portão segunda parte</t>
+  </si>
+  <si>
+    <t>Devolução INSS</t>
+  </si>
+  <si>
+    <t>Páscoa</t>
+  </si>
+  <si>
+    <t>Psicólogo Stella</t>
+  </si>
+  <si>
+    <t>Estadia Lucky</t>
+  </si>
+  <si>
+    <t>Completar INSS Maio</t>
+  </si>
+  <si>
+    <t>PS5 Samuel</t>
+  </si>
+  <si>
+    <t>Madero</t>
+  </si>
+  <si>
+    <t>Monitor Daniel</t>
+  </si>
+  <si>
+    <t>Nano</t>
+  </si>
+  <si>
+    <t>Conserto Meriva</t>
+  </si>
+  <si>
+    <t>Pagamento Capinha e si senor</t>
+  </si>
+  <si>
+    <t>Adiantamento ROG</t>
+  </si>
+  <si>
+    <t>Completar salário Junho</t>
+  </si>
+  <si>
+    <t>Gigio</t>
+  </si>
+  <si>
+    <t>Devolução Stella (325 do PS5)</t>
+  </si>
+  <si>
+    <t>Julho - Bônus</t>
+  </si>
+  <si>
+    <t>Julho - 40% 13º</t>
+  </si>
+  <si>
+    <t>Julho - Pagamentos Necessários</t>
+  </si>
+  <si>
+    <t>Pagamento Edilson</t>
+  </si>
+  <si>
+    <t>Ilumeo Julho - 1º PPT</t>
+  </si>
+  <si>
+    <t>Control+Dawnwalker</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>Ilumeo Agosto - 2º PPT</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>Passagens - Compradas em agosto</t>
+  </si>
+  <si>
+    <t>Restituição IR</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>Pagamento Control</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>Dawnwalker</t>
+  </si>
+  <si>
+    <t>Pagamento Dawnwalker</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>Ilumeo Dezembro - 3º PPT</t>
+  </si>
+  <si>
+    <t>Segunda Parcela 13º</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>Dinheiro para Europa</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>Ilumeo Maio - 4º PPT</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>Conta</t>
+  </si>
+  <si>
+    <t>Pago?</t>
+  </si>
+  <si>
+    <t>Obs.</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>Câmeras</t>
+  </si>
+  <si>
+    <t>NuBank</t>
+  </si>
+  <si>
     <t>Seu João</t>
   </si>
   <si>
-    <t>Seguro</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Com turbo</t>
-  </si>
-  <si>
-    <t>Caixinha Guilherme</t>
-  </si>
-  <si>
-    <t>Caixinha Stella</t>
-  </si>
-  <si>
-    <t>Sem turbo</t>
-  </si>
-  <si>
-    <t>IPVAs + Licenciamento</t>
-  </si>
-  <si>
-    <t>Tirando da Caixinha Turbo</t>
-  </si>
-  <si>
-    <t>Adiantamento Stella Janeiro</t>
-  </si>
-  <si>
-    <t>Devolução Stella</t>
-  </si>
-  <si>
-    <t>Ajuste NuConta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cidadania+Veterinário Brida </t>
-  </si>
-  <si>
-    <t>Salário afastamento</t>
-  </si>
-  <si>
-    <t>Emergência Geleia+Vurtuoso+Terra Brasa</t>
-  </si>
-  <si>
-    <t>Adiantamento Stella</t>
-  </si>
-  <si>
-    <t>Galpãozin</t>
-  </si>
-  <si>
-    <t>Fisioterapia Stella</t>
-  </si>
-  <si>
-    <t>Pagamento Fasolina + Almoço Shirley + Linkedin+Bonfas</t>
-  </si>
-  <si>
-    <t>INSS</t>
-  </si>
-  <si>
-    <t>Pagamento Superbowl</t>
-  </si>
-  <si>
-    <t>SiSenor</t>
-  </si>
-  <si>
-    <t>Alemão</t>
-  </si>
-  <si>
-    <t>Portão</t>
-  </si>
-  <si>
-    <t>Devolução  Stella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bonfa's </t>
-  </si>
-  <si>
-    <t>Ilumeo Março - WillBank</t>
-  </si>
-  <si>
-    <t>Remédio e Consulta Stella</t>
-  </si>
-  <si>
-    <t>Pagamentos</t>
-  </si>
-  <si>
-    <t>Adiantamento INSS</t>
-  </si>
-  <si>
-    <t>Adicional</t>
-  </si>
-  <si>
-    <t>Pagamentos fds Páscoa</t>
-  </si>
-  <si>
-    <t>Portão segunda parte</t>
-  </si>
-  <si>
-    <t>Devolução INSS</t>
-  </si>
-  <si>
-    <t>Páscoa</t>
-  </si>
-  <si>
-    <t>Psicólogo Stella</t>
-  </si>
-  <si>
-    <t>Estadia Lucky</t>
-  </si>
-  <si>
-    <t>Completar INSS Maio</t>
-  </si>
-  <si>
-    <t>PS5 Samuel</t>
-  </si>
-  <si>
-    <t>Madero</t>
-  </si>
-  <si>
-    <t>Monitor Daniel</t>
-  </si>
-  <si>
-    <t>Nano</t>
-  </si>
-  <si>
-    <t>Conserto Meriva</t>
-  </si>
-  <si>
-    <t>Pagamento Capinha e si senor</t>
-  </si>
-  <si>
-    <t>Adiantamento ROG</t>
-  </si>
-  <si>
-    <t>Completar salário Junho</t>
-  </si>
-  <si>
-    <t>Gigio</t>
-  </si>
-  <si>
-    <t>Devolução Stella (325 do PS5)</t>
-  </si>
-  <si>
-    <t>Julho - Bônus</t>
-  </si>
-  <si>
-    <t>Julho - 40% 13º</t>
-  </si>
-  <si>
-    <t>Julho - Pagamentos Necessários</t>
-  </si>
-  <si>
-    <t>Conta</t>
-  </si>
-  <si>
-    <t>Pago?</t>
-  </si>
-  <si>
-    <t>Obs.</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>Ok</t>
-  </si>
-  <si>
-    <t>Câmeras</t>
-  </si>
-  <si>
-    <t>NuBank</t>
-  </si>
-  <si>
     <t>Dera</t>
   </si>
   <si>
-    <t>Psicóloga</t>
-  </si>
-  <si>
-    <t>pontual</t>
-  </si>
-  <si>
-    <t>Reembolso Psicóloga</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Detran</t>
-  </si>
-  <si>
-    <t>Bonfas Chope</t>
-  </si>
-  <si>
-    <t>Cm</t>
-  </si>
-  <si>
-    <t>Bonfas Lanche</t>
-  </si>
-  <si>
-    <t>Remédios Stella</t>
-  </si>
-  <si>
-    <t>Ração Brida</t>
-  </si>
-  <si>
-    <t>Pagamento Ração Brida</t>
-  </si>
-  <si>
-    <t>Moletom Brutal Kill</t>
-  </si>
-  <si>
-    <t>TENTAR ADIATNAR</t>
-  </si>
-  <si>
-    <t>Uber Mr. Jones</t>
-  </si>
-  <si>
-    <t>Gibs</t>
-  </si>
-  <si>
-    <t>Serviço de nuvem da câmera</t>
-  </si>
-  <si>
-    <t>Gasolina</t>
-  </si>
-  <si>
-    <t>Rappi</t>
-  </si>
-  <si>
-    <t>Lanche</t>
-  </si>
-  <si>
-    <t>Control+Dawnwalker</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>Ilumeo Agosto - 2º PPT</t>
-  </si>
-  <si>
-    <t>Setembro</t>
-  </si>
-  <si>
-    <t>Restituição IR</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>Pagamento Control</t>
-  </si>
-  <si>
-    <t>Novembro</t>
-  </si>
-  <si>
-    <t>Dawnwalker</t>
-  </si>
-  <si>
-    <t>Pagamento Dawnwalker</t>
-  </si>
-  <si>
-    <t>Dinheiro para Europa</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>Junho</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>Ilumeo Dezembro - 3º PPT</t>
-  </si>
-  <si>
-    <t>Ilumeo Maio - 4º PPT</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
-    <t>Fevereiro</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>Ilumeo Julho - 1º PPT</t>
-  </si>
-  <si>
-    <t>Passagens - Compradas em agosto</t>
-  </si>
-  <si>
-    <t>Segunda Parcela 13º</t>
-  </si>
-  <si>
-    <t>Adiantamento Salário</t>
+    <t>Gibis</t>
+  </si>
+  <si>
+    <t>Bonffas Beer</t>
+  </si>
+  <si>
+    <t>Gasolina Pirassunusng</t>
+  </si>
+  <si>
+    <t>Hot Wheels</t>
+  </si>
+  <si>
+    <t>Pagamento Hot Wheels</t>
+  </si>
+  <si>
+    <t>Kikão</t>
+  </si>
+  <si>
+    <t>Gasolina de Volta</t>
+  </si>
+  <si>
+    <t>Odisseia</t>
+  </si>
+  <si>
+    <t>Pagamento Odisseia</t>
+  </si>
+  <si>
+    <t>Dinheiro Nano</t>
+  </si>
+  <si>
+    <t>Recolhimento Receita</t>
   </si>
 </sst>
 </file>
@@ -1209,17 +1245,7 @@
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1294,6 +1320,14 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79989013336588644"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E1F2"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1642,12 +1676,12 @@
       <c r="B3" s="78"/>
       <c r="C3" s="6">
         <f>C5-C8-C10-C11-C22+C23+C7</f>
-        <v>1879.5164047619041</v>
+        <v>1732.8714047619037</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="6">
         <f>E5-E8-E10-E11-E22+E23</f>
-        <v>3933.8625000000011</v>
+        <v>3729.3575000000001</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1669,12 +1703,12 @@
       </c>
       <c r="C6" s="8">
         <f>-SUM(C8,C10,C11)</f>
-        <v>-7458.4835952380963</v>
+        <v>-7605.1285952380968</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8">
         <f>-SUM(E8,E10,E11)</f>
-        <v>-5066.1374999999998</v>
+        <v>-5270.6424999999999</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -1705,12 +1739,12 @@
       </c>
       <c r="C9" s="8">
         <f>NuBank!E2</f>
-        <v>5036.2519285714288</v>
+        <v>5182.8969285714293</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8">
         <f>NuBank!F2</f>
-        <v>1684.0674999999999</v>
+        <v>1888.5724999999998</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -1719,12 +1753,12 @@
       </c>
       <c r="C10" s="11">
         <f>'Compensasões e Transferências'!D4</f>
-        <v>5036.2519285714288</v>
+        <v>5182.8969285714293</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="11">
         <f>'Compensasões e Transferências'!C4</f>
-        <v>1684.0674999999999</v>
+        <v>1888.5724999999998</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
@@ -2097,11 +2131,11 @@
       </c>
       <c r="C4" s="8">
         <f>Saldo!E9+C5</f>
-        <v>1684.0674999999999</v>
+        <v>1888.5724999999998</v>
       </c>
       <c r="D4" s="27">
         <f>Saldo!C9+D5</f>
-        <v>5036.2519285714288</v>
+        <v>5182.8969285714293</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
@@ -2205,7 +2239,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(C3,C4,C5,C10)</f>
-        <v>3731.7524999999996</v>
+        <v>3936.2574999999997</v>
       </c>
       <c r="D17" s="30"/>
     </row>
@@ -2929,7 +2963,7 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="J5:K22">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"Parcelado/Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2943,7 +2977,7 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="C1:Q151"/>
+  <dimension ref="C1:Q150"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
@@ -2977,19 +3011,19 @@
     </row>
     <row r="2" spans="3:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="48">
-        <f>SUM(L6:L378)</f>
-        <v>6770.3194285714271</v>
+        <f>SUM(L6:L377)</f>
+        <v>7121.4694285714277</v>
       </c>
       <c r="E2" s="35">
-        <f>SUMIF($E$6:$E$378,E1,$M$6:$M$378)</f>
-        <v>5036.2519285714288</v>
+        <f>SUMIF($E$6:$E$377,E1,$M$6:$M$377)</f>
+        <v>5182.8969285714293</v>
       </c>
       <c r="F2" s="35">
-        <f>SUMIF($F$6:$F$378,F1,$M$6:$M$378)</f>
-        <v>1684.0674999999999</v>
+        <f>SUMIF($F$6:$F$377,F1,$M$6:$M$377)</f>
+        <v>1888.5724999999998</v>
       </c>
       <c r="G2" s="35">
-        <f>SUMIF($G$6:$G$378,G1,$M$6:$M$378)</f>
+        <f>SUMIF($G$6:$G$377,G1,$M$6:$M$377)</f>
         <v>0</v>
       </c>
       <c r="L2" s="46"/>
@@ -4518,7 +4552,7 @@
       </c>
       <c r="G38" s="40"/>
       <c r="H38" s="40">
-        <f t="shared" ref="H38:H69" si="6">COUNTA(E38:G38)</f>
+        <f t="shared" ref="H38:H68" si="6">COUNTA(E38:G38)</f>
         <v>2</v>
       </c>
       <c r="I38" s="41">
@@ -4531,11 +4565,11 @@
         <v>74</v>
       </c>
       <c r="L38" s="41">
-        <f t="shared" ref="L38:L69" si="7">I38/N38</f>
+        <f t="shared" ref="L38:L68" si="7">I38/N38</f>
         <v>120.83333333333333</v>
       </c>
       <c r="M38" s="41">
-        <f t="shared" ref="M38:M69" si="8">IFERROR(L38/H38,"")</f>
+        <f t="shared" ref="M38:M68" si="8">IFERROR(L38/H38,"")</f>
         <v>60.416666666666664</v>
       </c>
       <c r="N38" s="42">
@@ -4545,7 +4579,7 @@
         <v>46145</v>
       </c>
       <c r="P38" s="67">
-        <f t="shared" ref="P38:P69" si="9">IF(N38&lt;&gt;1,EDATE(O38,N38-1),"")</f>
+        <f t="shared" ref="P38:P68" si="9">IF(N38&lt;&gt;1,EDATE(O38,N38-1),"")</f>
         <v>46298</v>
       </c>
       <c r="Q38" s="40">
@@ -4778,7 +4812,7 @@
         <v>46421</v>
       </c>
       <c r="Q43" s="40">
-        <f t="shared" ref="Q43:Q74" ca="1" si="10">IF(O43&lt;&gt;"",IFERROR(DATEDIF(O43,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ref="Q43:Q73" ca="1" si="10">IF(O43&lt;&gt;"",IFERROR(DATEDIF(O43,TODAY(),"m")+1,""),"")</f>
         <v>3</v>
       </c>
     </row>
@@ -5285,7 +5319,7 @@
     <row r="55" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C55" s="38"/>
       <c r="D55" s="49" t="s">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="E55" s="40" t="s">
         <v>1</v>
@@ -5300,7 +5334,7 @@
         <v>498</v>
       </c>
       <c r="J55" s="41" t="s">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="K55" s="41" t="s">
         <v>52</v>
@@ -5329,7 +5363,7 @@
     <row r="56" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C56" s="38"/>
       <c r="D56" s="49" t="s">
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="E56" s="40" t="s">
         <v>1</v>
@@ -5349,7 +5383,7 @@
         <v>108</v>
       </c>
       <c r="K56" s="41" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="L56" s="41">
         <f t="shared" si="7"/>
@@ -5375,7 +5409,7 @@
     <row r="57" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C57" s="38"/>
       <c r="D57" s="49" t="s">
-        <v>185</v>
+        <v>113</v>
       </c>
       <c r="E57" s="40" t="s">
         <v>1</v>
@@ -5415,7 +5449,7 @@
     <row r="58" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C58" s="38"/>
       <c r="D58" s="49" t="s">
-        <v>186</v>
+        <v>114</v>
       </c>
       <c r="E58" s="40"/>
       <c r="F58" s="40" t="s">
@@ -5455,7 +5489,7 @@
     <row r="59" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C59" s="38"/>
       <c r="D59" s="49" t="s">
-        <v>187</v>
+        <v>115</v>
       </c>
       <c r="E59" s="40" t="s">
         <v>1</v>
@@ -5497,7 +5531,7 @@
     <row r="60" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C60" s="38"/>
       <c r="D60" s="49" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="E60" s="40" t="s">
         <v>1</v>
@@ -5536,10 +5570,10 @@
     </row>
     <row r="61" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C61" s="38" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="E61" s="40" t="s">
         <v>1</v>
@@ -5583,7 +5617,7 @@
     <row r="62" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C62" s="38"/>
       <c r="D62" s="49" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="E62" s="40" t="s">
         <v>1</v>
@@ -5625,7 +5659,7 @@
     <row r="63" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C63" s="38"/>
       <c r="D63" s="49" t="s">
-        <v>192</v>
+        <v>120</v>
       </c>
       <c r="E63" s="40" t="s">
         <v>1</v>
@@ -5665,7 +5699,7 @@
     <row r="64" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C64" s="38"/>
       <c r="D64" s="49" t="s">
-        <v>193</v>
+        <v>121</v>
       </c>
       <c r="E64" s="40" t="s">
         <v>1</v>
@@ -5707,7 +5741,7 @@
     <row r="65" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C65" s="38"/>
       <c r="D65" s="49" t="s">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="E65" s="40" t="s">
         <v>1</v>
@@ -5721,17 +5755,17 @@
         <v>2</v>
       </c>
       <c r="I65" s="41">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="J65" s="41"/>
       <c r="K65" s="41"/>
       <c r="L65" s="41">
         <f t="shared" si="7"/>
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="M65" s="41">
         <f t="shared" si="8"/>
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="N65" s="42">
         <v>1</v>
@@ -5749,31 +5783,29 @@
     <row r="66" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C66" s="38"/>
       <c r="D66" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="E66" s="40" t="s">
-        <v>1</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="E66" s="40"/>
       <c r="F66" s="40" t="s">
         <v>2</v>
       </c>
       <c r="G66" s="40"/>
       <c r="H66" s="40">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I66" s="41">
-        <v>74</v>
+        <v>107.5</v>
       </c>
       <c r="J66" s="41"/>
       <c r="K66" s="41"/>
       <c r="L66" s="41">
         <f t="shared" si="7"/>
-        <v>74</v>
+        <v>107.5</v>
       </c>
       <c r="M66" s="41">
         <f t="shared" si="8"/>
-        <v>37</v>
+        <v>107.5</v>
       </c>
       <c r="N66" s="42">
         <v>1</v>
@@ -5791,29 +5823,29 @@
     <row r="67" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C67" s="38"/>
       <c r="D67" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="E67" s="40"/>
-      <c r="F67" s="40" t="s">
-        <v>2</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="E67" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F67" s="40"/>
       <c r="G67" s="40"/>
       <c r="H67" s="40">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I67" s="41">
-        <v>107.5</v>
+        <v>37.5</v>
       </c>
       <c r="J67" s="41"/>
       <c r="K67" s="41"/>
       <c r="L67" s="41">
         <f t="shared" si="7"/>
-        <v>107.5</v>
+        <v>37.5</v>
       </c>
       <c r="M67" s="41">
         <f t="shared" si="8"/>
-        <v>107.5</v>
+        <v>37.5</v>
       </c>
       <c r="N67" s="42">
         <v>1</v>
@@ -5831,7 +5863,7 @@
     <row r="68" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C68" s="38"/>
       <c r="D68" s="49" t="s">
-        <v>194</v>
+        <v>124</v>
       </c>
       <c r="E68" s="40" t="s">
         <v>1</v>
@@ -5843,23 +5875,23 @@
         <v>1</v>
       </c>
       <c r="I68" s="41">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="J68" s="41"/>
       <c r="K68" s="41"/>
       <c r="L68" s="41">
         <f t="shared" si="7"/>
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="M68" s="41">
         <f t="shared" si="8"/>
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="N68" s="42">
         <v>1</v>
       </c>
-      <c r="O68" s="67"/>
-      <c r="P68" s="67" t="str">
+      <c r="O68" s="38"/>
+      <c r="P68" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -5871,7 +5903,7 @@
     <row r="69" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C69" s="38"/>
       <c r="D69" s="49" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="E69" s="40" t="s">
         <v>1</v>
@@ -5879,28 +5911,28 @@
       <c r="F69" s="40"/>
       <c r="G69" s="40"/>
       <c r="H69" s="40">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="H69:H100" si="11">COUNTA(E69:G69)</f>
         <v>1</v>
       </c>
       <c r="I69" s="41">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J69" s="41"/>
       <c r="K69" s="41"/>
       <c r="L69" s="41">
-        <f t="shared" si="7"/>
-        <v>50</v>
+        <f t="shared" ref="L69:L100" si="12">I69/N69</f>
+        <v>35</v>
       </c>
       <c r="M69" s="41">
-        <f t="shared" si="8"/>
-        <v>50</v>
+        <f t="shared" ref="M69:M100" si="13">IFERROR(L69/H69,"")</f>
+        <v>35</v>
       </c>
       <c r="N69" s="42">
         <v>1</v>
       </c>
       <c r="O69" s="38"/>
       <c r="P69" s="38" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="P69:P100" si="14">IF(N69&lt;&gt;1,EDATE(O69,N69-1),"")</f>
         <v/>
       </c>
       <c r="Q69" s="40" t="str">
@@ -5910,31 +5942,37 @@
     </row>
     <row r="70" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C70" s="38"/>
-      <c r="D70" s="49"/>
-      <c r="E70" s="40"/>
+      <c r="D70" s="49" t="s">
+        <v>224</v>
+      </c>
+      <c r="E70" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F70" s="40"/>
       <c r="G70" s="40"/>
       <c r="H70" s="40">
-        <f t="shared" ref="H70:H101" si="11">COUNTA(E70:G70)</f>
-        <v>0</v>
-      </c>
-      <c r="I70" s="41"/>
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="I70" s="41">
+        <v>52.14</v>
+      </c>
       <c r="J70" s="41"/>
       <c r="K70" s="41"/>
       <c r="L70" s="41">
-        <f t="shared" ref="L70:L101" si="12">I70/N70</f>
-        <v>0</v>
-      </c>
-      <c r="M70" s="41" t="str">
-        <f t="shared" ref="M70:M101" si="13">IFERROR(L70/H70,"")</f>
-        <v/>
+        <f t="shared" si="12"/>
+        <v>52.14</v>
+      </c>
+      <c r="M70" s="41">
+        <f t="shared" si="13"/>
+        <v>52.14</v>
       </c>
       <c r="N70" s="42">
         <v>1</v>
       </c>
       <c r="O70" s="38"/>
       <c r="P70" s="38" t="str">
-        <f t="shared" ref="P70:P101" si="14">IF(N70&lt;&gt;1,EDATE(O70,N70-1),"")</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="Q70" s="40" t="str">
@@ -5944,24 +5982,32 @@
     </row>
     <row r="71" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C71" s="38"/>
-      <c r="D71" s="49"/>
-      <c r="E71" s="40"/>
-      <c r="F71" s="40"/>
+      <c r="D71" s="49" t="s">
+        <v>225</v>
+      </c>
+      <c r="E71" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F71" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G71" s="40"/>
       <c r="H71" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I71" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I71" s="41">
+        <v>130.01</v>
+      </c>
       <c r="J71" s="41"/>
       <c r="K71" s="41"/>
       <c r="L71" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M71" s="41" t="str">
+        <v>130.01</v>
+      </c>
+      <c r="M71" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>65.004999999999995</v>
       </c>
       <c r="N71" s="42">
         <v>1</v>
@@ -5978,24 +6024,30 @@
     </row>
     <row r="72" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C72" s="38"/>
-      <c r="D72" s="49"/>
-      <c r="E72" s="40"/>
+      <c r="D72" s="49" t="s">
+        <v>226</v>
+      </c>
+      <c r="E72" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F72" s="40"/>
       <c r="G72" s="40"/>
       <c r="H72" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I72" s="41"/>
+        <v>1</v>
+      </c>
+      <c r="I72" s="41">
+        <v>99</v>
+      </c>
       <c r="J72" s="41"/>
       <c r="K72" s="41"/>
       <c r="L72" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M72" s="41" t="str">
+        <v>99</v>
+      </c>
+      <c r="M72" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>99</v>
       </c>
       <c r="N72" s="42">
         <v>1</v>
@@ -6012,24 +6064,30 @@
     </row>
     <row r="73" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C73" s="38"/>
-      <c r="D73" s="49"/>
-      <c r="E73" s="40"/>
+      <c r="D73" s="49" t="s">
+        <v>227</v>
+      </c>
+      <c r="E73" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F73" s="40"/>
       <c r="G73" s="40"/>
       <c r="H73" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="41"/>
+        <v>1</v>
+      </c>
+      <c r="I73" s="41">
+        <v>-99</v>
+      </c>
       <c r="J73" s="41"/>
       <c r="K73" s="41"/>
       <c r="L73" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M73" s="41" t="str">
+        <v>-99</v>
+      </c>
+      <c r="M73" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-99</v>
       </c>
       <c r="N73" s="42">
         <v>1</v>
@@ -6046,24 +6104,32 @@
     </row>
     <row r="74" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C74" s="38"/>
-      <c r="D74" s="49"/>
-      <c r="E74" s="40"/>
-      <c r="F74" s="40"/>
+      <c r="D74" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="E74" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F74" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G74" s="40"/>
       <c r="H74" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I74" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I74" s="41">
+        <v>139</v>
+      </c>
       <c r="J74" s="41"/>
       <c r="K74" s="41"/>
       <c r="L74" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M74" s="41" t="str">
+        <v>139</v>
+      </c>
+      <c r="M74" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>69.5</v>
       </c>
       <c r="N74" s="42">
         <v>1</v>
@@ -6074,30 +6140,36 @@
         <v/>
       </c>
       <c r="Q74" s="40" t="str">
-        <f t="shared" ca="1" si="10"/>
+        <f t="shared" ref="Q74:Q105" ca="1" si="15">IF(O74&lt;&gt;"",IFERROR(DATEDIF(O74,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="75" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C75" s="38"/>
-      <c r="D75" s="49"/>
+      <c r="D75" s="49" t="s">
+        <v>229</v>
+      </c>
       <c r="E75" s="40"/>
-      <c r="F75" s="40"/>
+      <c r="F75" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G75" s="40"/>
       <c r="H75" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I75" s="41"/>
+        <v>1</v>
+      </c>
+      <c r="I75" s="41">
+        <v>100</v>
+      </c>
       <c r="J75" s="41"/>
       <c r="K75" s="41"/>
       <c r="L75" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M75" s="41" t="str">
+        <v>100</v>
+      </c>
+      <c r="M75" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>100</v>
       </c>
       <c r="N75" s="42">
         <v>1</v>
@@ -6108,30 +6180,38 @@
         <v/>
       </c>
       <c r="Q75" s="40" t="str">
-        <f t="shared" ref="Q75:Q106" ca="1" si="15">IF(O75&lt;&gt;"",IFERROR(DATEDIF(O75,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
     </row>
     <row r="76" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C76" s="38"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="40"/>
-      <c r="F76" s="40"/>
+      <c r="D76" s="49" t="s">
+        <v>230</v>
+      </c>
+      <c r="E76" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F76" s="40" t="s">
+        <v>2</v>
+      </c>
       <c r="G76" s="40"/>
       <c r="H76" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I76" s="41"/>
+        <v>2</v>
+      </c>
+      <c r="I76" s="41">
+        <v>90</v>
+      </c>
       <c r="J76" s="41"/>
       <c r="K76" s="41"/>
       <c r="L76" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M76" s="41" t="str">
+        <v>90</v>
+      </c>
+      <c r="M76" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>45</v>
       </c>
       <c r="N76" s="42">
         <v>1</v>
@@ -6148,24 +6228,30 @@
     </row>
     <row r="77" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C77" s="38"/>
-      <c r="D77" s="49"/>
-      <c r="E77" s="40"/>
+      <c r="D77" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E77" s="40" t="s">
+        <v>1</v>
+      </c>
       <c r="F77" s="40"/>
       <c r="G77" s="40"/>
       <c r="H77" s="40">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I77" s="41"/>
+        <v>1</v>
+      </c>
+      <c r="I77" s="41">
+        <v>-45</v>
+      </c>
       <c r="J77" s="41"/>
       <c r="K77" s="41"/>
       <c r="L77" s="41">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M77" s="41" t="str">
+        <v>-45</v>
+      </c>
+      <c r="M77" s="41">
         <f t="shared" si="13"/>
-        <v/>
+        <v>-45</v>
       </c>
       <c r="N77" s="42">
         <v>1</v>
@@ -6969,18 +7055,18 @@
       <c r="F101" s="40"/>
       <c r="G101" s="40"/>
       <c r="H101" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="H101:H132" si="16">COUNTA(E101:G101)</f>
         <v>0</v>
       </c>
       <c r="I101" s="41"/>
       <c r="J101" s="41"/>
       <c r="K101" s="41"/>
       <c r="L101" s="41">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="L101:L132" si="17">I101/N101</f>
         <v>0</v>
       </c>
       <c r="M101" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="M101:M132" si="18">IFERROR(L101/H101,"")</f>
         <v/>
       </c>
       <c r="N101" s="42">
@@ -6988,7 +7074,7 @@
       </c>
       <c r="O101" s="38"/>
       <c r="P101" s="38" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="P101:P132" si="19">IF(N101&lt;&gt;1,EDATE(O101,N101-1),"")</f>
         <v/>
       </c>
       <c r="Q101" s="40" t="str">
@@ -7003,18 +7089,18 @@
       <c r="F102" s="40"/>
       <c r="G102" s="40"/>
       <c r="H102" s="40">
-        <f t="shared" ref="H102:H133" si="16">COUNTA(E102:G102)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I102" s="41"/>
       <c r="J102" s="41"/>
       <c r="K102" s="41"/>
       <c r="L102" s="41">
-        <f t="shared" ref="L102:L133" si="17">I102/N102</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M102" s="41" t="str">
-        <f t="shared" ref="M102:M133" si="18">IFERROR(L102/H102,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N102" s="42">
@@ -7022,7 +7108,7 @@
       </c>
       <c r="O102" s="38"/>
       <c r="P102" s="38" t="str">
-        <f t="shared" ref="P102:P133" si="19">IF(N102&lt;&gt;1,EDATE(O102,N102-1),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q102" s="40" t="str">
@@ -7162,7 +7248,7 @@
         <v/>
       </c>
       <c r="Q106" s="40" t="str">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" ref="Q106:Q137" ca="1" si="20">IF(O106&lt;&gt;"",IFERROR(DATEDIF(O106,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -7196,7 +7282,7 @@
         <v/>
       </c>
       <c r="Q107" s="40" t="str">
-        <f t="shared" ref="Q107:Q138" ca="1" si="20">IF(O107&lt;&gt;"",IFERROR(DATEDIF(O107,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="20"/>
         <v/>
       </c>
     </row>
@@ -8057,18 +8143,18 @@
       <c r="F133" s="40"/>
       <c r="G133" s="40"/>
       <c r="H133" s="40">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="H133:H149" si="21">COUNTA(E133:G133)</f>
         <v>0</v>
       </c>
       <c r="I133" s="41"/>
       <c r="J133" s="41"/>
       <c r="K133" s="41"/>
       <c r="L133" s="41">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="L133:L149" si="22">I133/N133</f>
         <v>0</v>
       </c>
       <c r="M133" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="M133:M149" si="23">IFERROR(L133/H133,"")</f>
         <v/>
       </c>
       <c r="N133" s="42">
@@ -8076,7 +8162,7 @@
       </c>
       <c r="O133" s="38"/>
       <c r="P133" s="38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="P133:P149" si="24">IF(N133&lt;&gt;1,EDATE(O133,N133-1),"")</f>
         <v/>
       </c>
       <c r="Q133" s="40" t="str">
@@ -8091,18 +8177,18 @@
       <c r="F134" s="40"/>
       <c r="G134" s="40"/>
       <c r="H134" s="40">
-        <f t="shared" ref="H134:H150" si="21">COUNTA(E134:G134)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I134" s="41"/>
       <c r="J134" s="41"/>
       <c r="K134" s="41"/>
       <c r="L134" s="41">
-        <f t="shared" ref="L134:L150" si="22">I134/N134</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M134" s="41" t="str">
-        <f t="shared" ref="M134:M150" si="23">IFERROR(L134/H134,"")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="N134" s="42">
@@ -8110,7 +8196,7 @@
       </c>
       <c r="O134" s="38"/>
       <c r="P134" s="38" t="str">
-        <f t="shared" ref="P134:P150" si="24">IF(N134&lt;&gt;1,EDATE(O134,N134-1),"")</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="Q134" s="40" t="str">
@@ -8250,7 +8336,7 @@
         <v/>
       </c>
       <c r="Q138" s="40" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ref="Q138:Q149" ca="1" si="25">IF(O138&lt;&gt;"",IFERROR(DATEDIF(O138,TODAY(),"m")+1,""),"")</f>
         <v/>
       </c>
     </row>
@@ -8284,7 +8370,7 @@
         <v/>
       </c>
       <c r="Q139" s="40" t="str">
-        <f t="shared" ref="Q139:Q150" ca="1" si="25">IF(O139&lt;&gt;"",IFERROR(DATEDIF(O139,TODAY(),"m")+1,""),"")</f>
+        <f t="shared" ca="1" si="25"/>
         <v/>
       </c>
     </row>
@@ -8584,7 +8670,7 @@
       <c r="N148" s="42">
         <v>1</v>
       </c>
-      <c r="O148" s="38"/>
+      <c r="O148" s="44"/>
       <c r="P148" s="38" t="str">
         <f t="shared" si="24"/>
         <v/>
@@ -8618,7 +8704,7 @@
       <c r="N149" s="42">
         <v>1</v>
       </c>
-      <c r="O149" s="44"/>
+      <c r="O149" s="38"/>
       <c r="P149" s="38" t="str">
         <f t="shared" si="24"/>
         <v/>
@@ -8634,69 +8720,35 @@
       <c r="E150" s="40"/>
       <c r="F150" s="40"/>
       <c r="G150" s="40"/>
-      <c r="H150" s="40">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
+      <c r="H150" s="40"/>
       <c r="I150" s="41"/>
       <c r="J150" s="41"/>
       <c r="K150" s="41"/>
-      <c r="L150" s="41">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="M150" s="41" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="N150" s="42">
-        <v>1</v>
-      </c>
-      <c r="O150" s="38"/>
-      <c r="P150" s="38" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="Q150" s="40" t="str">
-        <f t="shared" ca="1" si="25"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C151" s="38"/>
-      <c r="D151" s="49"/>
-      <c r="E151" s="40"/>
-      <c r="F151" s="40"/>
-      <c r="G151" s="40"/>
-      <c r="H151" s="40"/>
-      <c r="I151" s="41"/>
-      <c r="J151" s="41"/>
-      <c r="K151" s="41"/>
-      <c r="L151" s="41"/>
-      <c r="M151" s="41"/>
-      <c r="N151" s="42"/>
-      <c r="O151" s="67"/>
-      <c r="P151" s="67"/>
-      <c r="Q151" s="40"/>
+      <c r="L150" s="41"/>
+      <c r="M150" s="41"/>
+      <c r="N150" s="42"/>
+      <c r="O150" s="67"/>
+      <c r="P150" s="67"/>
+      <c r="Q150" s="40"/>
     </row>
   </sheetData>
-  <autoFilter ref="C5:Q151" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q151">
-      <sortCondition sortBy="cellColor" ref="J5:J151" dxfId="16"/>
+  <autoFilter ref="C5:Q150" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C6:Q150">
+      <sortCondition sortBy="cellColor" ref="J5:J150" dxfId="15"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="I6:I151">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="lessThan">
+  <conditionalFormatting sqref="I6:I150">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J151">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+  <conditionalFormatting sqref="J6:J150">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
       <formula>"Assinatura"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:K151">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+  <conditionalFormatting sqref="J6:K150">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"Parcelado"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8799,7 +8851,7 @@
     </row>
     <row r="4" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="58" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E4" s="59" t="s">
         <v>1</v>
@@ -8840,7 +8892,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="E5" s="39" t="s">
         <v>1</v>
@@ -8882,7 +8934,7 @@
         <v>2382.0700000000002</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="E6" s="39" t="s">
         <v>1</v>
@@ -8920,7 +8972,7 @@
     <row r="7" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="63"/>
       <c r="D7" s="57" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="E7" s="39" t="s">
         <v>1</v>
@@ -9001,7 +9053,7 @@
         <v>3382.07</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="E9" s="39" t="s">
         <v>1</v>
@@ -9039,7 +9091,7 @@
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D10" s="57" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="E10" s="39"/>
       <c r="F10" s="40" t="s">
@@ -9240,7 +9292,7 @@
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" s="2"/>
       <c r="N1" s="50" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9250,10 +9302,10 @@
     <row r="3" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G3" s="2"/>
       <c r="L3" s="50" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="M3" s="75" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="N3" s="46">
         <f>SUM(N5:N21)</f>
@@ -9264,7 +9316,7 @@
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G4" s="2"/>
       <c r="L4" s="51" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="M4" s="76"/>
       <c r="N4" s="52"/>
@@ -9275,7 +9327,7 @@
       <c r="F5" s="16"/>
       <c r="G5" s="31"/>
       <c r="L5" t="s">
-        <v>221</v>
+        <v>135</v>
       </c>
       <c r="N5" s="1">
         <v>4912</v>
@@ -9285,7 +9337,7 @@
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G6" s="2"/>
       <c r="L6" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="N6" s="1">
         <v>101</v>
@@ -9299,10 +9351,10 @@
       <c r="F8" s="16"/>
       <c r="G8" s="53"/>
       <c r="L8" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="M8" t="s">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="N8" s="1">
         <v>338</v>
@@ -9310,41 +9362,41 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F9" s="50" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="G9" s="31"/>
       <c r="N9" s="46"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="F10" s="16">
         <f>SUM(G11:I11)</f>
-        <v>1765.1500000000015</v>
+        <v>164.15000000000146</v>
       </c>
       <c r="G10" s="54" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="H10" s="54" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="I10" s="54" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="N10" s="46"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="F11" s="16">
         <f>SUM(G11:H11)</f>
-        <v>1765.1500000000015</v>
+        <v>164.15000000000146</v>
       </c>
       <c r="G11" s="1">
         <f>G12+SUM(G14:G496)</f>
-        <v>1765.1500000000015</v>
+        <v>164.15000000000146</v>
       </c>
       <c r="H11" s="1">
         <f>H12+SUM(H14:H496)</f>
@@ -9358,7 +9410,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="G12" s="1">
         <v>15250</v>
@@ -9367,7 +9419,7 @@
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F13" s="74" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="G13" s="55"/>
       <c r="H13" s="74"/>
@@ -9378,7 +9430,7 @@
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
       <c r="F14" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="56"/>
@@ -9389,7 +9441,7 @@
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
       <c r="F15" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="G15" s="56">
         <v>773.35</v>
@@ -9402,7 +9454,7 @@
       <c r="C16" s="56"/>
       <c r="D16" s="56"/>
       <c r="F16" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="G16" s="56">
         <v>-5148</v>
@@ -9415,7 +9467,7 @@
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
       <c r="F17" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="G17" s="56">
         <v>-168</v>
@@ -9428,7 +9480,7 @@
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
       <c r="F18" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="G18" s="56">
         <v>-1700</v>
@@ -9441,7 +9493,7 @@
       <c r="C19" s="56"/>
       <c r="D19" s="56"/>
       <c r="F19" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="G19" s="56">
         <v>5148</v>
@@ -9454,7 +9506,7 @@
       <c r="C20" s="56"/>
       <c r="D20" s="56"/>
       <c r="F20" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="G20" s="56">
         <v>-4938</v>
@@ -9467,7 +9519,7 @@
       <c r="C21" s="56"/>
       <c r="D21" s="56"/>
       <c r="F21" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="G21" s="56">
         <v>-1595</v>
@@ -9480,7 +9532,7 @@
       <c r="C22" s="56"/>
       <c r="D22" s="56"/>
       <c r="F22" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="G22" s="56">
         <v>-4677</v>
@@ -9493,7 +9545,7 @@
       <c r="C23" s="56"/>
       <c r="D23" s="56"/>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="G23" s="56">
         <v>-200</v>
@@ -9506,7 +9558,7 @@
       <c r="C24" s="56"/>
       <c r="D24" s="56"/>
       <c r="F24" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="G24" s="56">
         <v>4677</v>
@@ -9519,7 +9571,7 @@
       <c r="C25" s="56"/>
       <c r="D25" s="56"/>
       <c r="F25" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="G25" s="56">
         <v>-750</v>
@@ -9532,7 +9584,7 @@
       <c r="C26" s="56"/>
       <c r="D26" s="56"/>
       <c r="F26" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="G26" s="56">
         <v>-652</v>
@@ -9545,7 +9597,7 @@
       <c r="C27" s="56"/>
       <c r="D27" s="56"/>
       <c r="F27" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="G27" s="56">
         <v>11100</v>
@@ -9558,7 +9610,7 @@
       <c r="C28" s="56"/>
       <c r="D28" s="56"/>
       <c r="F28" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="G28" s="56">
         <v>-396</v>
@@ -9571,7 +9623,7 @@
       <c r="C29" s="56"/>
       <c r="D29" s="56"/>
       <c r="F29" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="G29" s="56">
         <v>-4211</v>
@@ -9584,7 +9636,7 @@
       <c r="C30" s="56"/>
       <c r="D30" s="56"/>
       <c r="F30" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="G30" s="56">
         <v>-450</v>
@@ -9597,7 +9649,7 @@
       <c r="C31" s="56"/>
       <c r="D31" s="56"/>
       <c r="F31" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="G31" s="56">
         <v>-1197</v>
@@ -9623,7 +9675,7 @@
       <c r="C33" s="56"/>
       <c r="D33" s="56"/>
       <c r="F33" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G33" s="56">
         <v>-830</v>
@@ -9636,7 +9688,7 @@
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
       <c r="F34" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="G34" s="56">
         <v>4211</v>
@@ -9649,7 +9701,7 @@
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
       <c r="F35" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="G35" s="56">
         <v>-200</v>
@@ -9662,7 +9714,7 @@
       <c r="C36" s="56"/>
       <c r="D36" s="56"/>
       <c r="F36" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="G36" s="56">
         <v>10000</v>
@@ -9675,7 +9727,7 @@
       <c r="C37" s="56"/>
       <c r="D37" s="56"/>
       <c r="F37" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="G37" s="56">
         <v>-200</v>
@@ -9688,7 +9740,7 @@
       <c r="C38" s="56"/>
       <c r="D38" s="56"/>
       <c r="F38" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G38" s="56">
         <v>-381</v>
@@ -9701,7 +9753,7 @@
       <c r="C39" s="56"/>
       <c r="D39" s="56"/>
       <c r="F39" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="G39" s="56">
         <v>-4911</v>
@@ -9715,7 +9767,7 @@
       <c r="D40" s="56"/>
       <c r="E40" s="2"/>
       <c r="F40" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="G40" s="56">
         <v>-5700</v>
@@ -9728,7 +9780,7 @@
       <c r="C41" s="56"/>
       <c r="D41" s="56"/>
       <c r="F41" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="G41" s="56">
         <v>-400</v>
@@ -9741,7 +9793,7 @@
       <c r="C42" s="56"/>
       <c r="D42" s="56"/>
       <c r="F42" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="G42" s="56">
         <v>-450</v>
@@ -9754,7 +9806,7 @@
       <c r="C43" s="56"/>
       <c r="D43" s="56"/>
       <c r="F43" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="G43" s="56">
         <v>-640</v>
@@ -9768,7 +9820,7 @@
       <c r="D44" s="56"/>
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="G44" s="56">
         <v>5700</v>
@@ -9781,7 +9833,7 @@
       <c r="C45" s="56"/>
       <c r="D45" s="56"/>
       <c r="F45" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="G45" s="56">
         <v>-130</v>
@@ -9794,7 +9846,7 @@
       <c r="C46" s="56"/>
       <c r="D46" s="56"/>
       <c r="F46" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="G46" s="56">
         <v>-250</v>
@@ -9807,7 +9859,7 @@
       <c r="C47" s="56"/>
       <c r="D47" s="56"/>
       <c r="F47" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="G47" s="56">
         <v>-112.2</v>
@@ -9820,7 +9872,7 @@
       <c r="C48" s="56"/>
       <c r="D48" s="56"/>
       <c r="F48" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="G48" s="56">
         <v>4911</v>
@@ -9833,7 +9885,7 @@
       <c r="C49" s="56"/>
       <c r="D49" s="56"/>
       <c r="F49" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="G49" s="56">
         <v>-3000</v>
@@ -9846,7 +9898,7 @@
       <c r="C50" s="56"/>
       <c r="D50" s="56"/>
       <c r="F50" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="G50" s="56">
         <v>-4000</v>
@@ -9859,7 +9911,7 @@
       <c r="C51" s="56"/>
       <c r="D51" s="56"/>
       <c r="F51" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="G51" s="56">
         <v>-200</v>
@@ -9872,7 +9924,7 @@
       <c r="C52" s="56"/>
       <c r="D52" s="56"/>
       <c r="F52" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="G52" s="56">
         <v>-4612</v>
@@ -9883,7 +9935,7 @@
     </row>
     <row r="53" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F53" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="G53" s="56">
         <v>-700</v>
@@ -9894,7 +9946,7 @@
     </row>
     <row r="54" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F54" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G54" s="56">
         <v>-880</v>
@@ -9905,7 +9957,7 @@
     </row>
     <row r="55" spans="3:14" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="F55" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G55" s="56">
         <v>-310</v>
@@ -9916,7 +9968,7 @@
     </row>
     <row r="56" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F56" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="G56" s="56">
         <v>-250</v>
@@ -9927,7 +9979,7 @@
     </row>
     <row r="57" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F57" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="G57" s="56">
         <v>4690</v>
@@ -9938,7 +9990,7 @@
     </row>
     <row r="58" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F58" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="G58" s="56">
         <v>-4440</v>
@@ -9949,7 +10001,7 @@
     </row>
     <row r="59" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F59" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="G59" s="56">
         <v>-4697</v>
@@ -9959,7 +10011,7 @@
     </row>
     <row r="60" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F60" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="G60" s="56">
         <v>-2500</v>
@@ -9969,7 +10021,7 @@
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F61" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="G61" s="56">
         <v>-126</v>
@@ -9979,7 +10031,7 @@
     </row>
     <row r="62" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F62" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="G62" s="56">
         <v>4742</v>
@@ -9989,7 +10041,7 @@
     </row>
     <row r="63" spans="3:14" x14ac:dyDescent="0.25">
       <c r="F63" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G63" s="56">
         <v>-410</v>
@@ -10004,7 +10056,7 @@
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F65" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="G65" s="56">
         <v>3320</v>
@@ -10014,7 +10066,7 @@
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F66" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="G66" s="56">
         <v>4090</v>
@@ -10024,7 +10076,7 @@
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F67" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="G67" s="56">
         <v>-5688</v>
@@ -10034,7 +10086,7 @@
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F68" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="G68" s="56">
         <v>-4433</v>
@@ -10043,77 +10095,72 @@
       <c r="I68" s="56"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="G69" s="56"/>
+      <c r="F69" t="s">
+        <v>189</v>
+      </c>
+      <c r="G69" s="56">
+        <v>-250</v>
+      </c>
       <c r="H69" s="56"/>
       <c r="I69" s="56"/>
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C70" s="56"/>
       <c r="D70" s="56"/>
-      <c r="G70" s="56"/>
+      <c r="F70" t="s">
+        <v>226</v>
+      </c>
+      <c r="G70" s="56">
+        <v>-99</v>
+      </c>
       <c r="H70" s="56"/>
       <c r="I70" s="56"/>
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
-        <v>129</v>
-      </c>
-      <c r="C71" s="56">
-        <v>4433</v>
-      </c>
-      <c r="D71" s="56"/>
-      <c r="G71" s="56"/>
+      <c r="F71" t="s">
+        <v>232</v>
+      </c>
+      <c r="G71" s="56">
+        <v>320</v>
+      </c>
       <c r="H71" s="56"/>
       <c r="I71" s="56"/>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B72" t="s">
-        <v>218</v>
-      </c>
-      <c r="C72" s="56">
-        <v>8000</v>
-      </c>
-      <c r="D72" s="56"/>
-      <c r="G72" s="56"/>
+      <c r="F72" t="s">
+        <v>233</v>
+      </c>
+      <c r="G72" s="56">
+        <v>-1572</v>
+      </c>
       <c r="H72" s="56"/>
       <c r="I72" s="56"/>
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C73" s="56"/>
-      <c r="D73" s="56"/>
       <c r="G73" s="56"/>
       <c r="H73" s="56"/>
       <c r="I73" s="56"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B74" t="s">
-        <v>197</v>
-      </c>
-      <c r="C74" s="56">
-        <v>-90</v>
-      </c>
-      <c r="D74" s="56"/>
       <c r="G74" s="56"/>
       <c r="H74" s="56"/>
       <c r="I74" s="56"/>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c r="C75" s="56">
-        <v>1000</v>
-      </c>
-      <c r="D75" s="56">
-        <v>300</v>
-      </c>
+        <v>4433</v>
+      </c>
+      <c r="D75" s="56"/>
       <c r="G75" s="56"/>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C76" s="56">
         <v>8000</v>
@@ -10132,7 +10179,7 @@
     </row>
     <row r="78" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C78" s="56">
         <v>-90</v>
@@ -10144,10 +10191,10 @@
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C79" s="56">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="D79" s="56">
         <v>300</v>
@@ -10158,10 +10205,10 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="C80" s="56">
-        <v>-12807</v>
+        <v>8000</v>
       </c>
       <c r="D80" s="56"/>
       <c r="G80" s="56"/>
@@ -10177,10 +10224,10 @@
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C82" s="56">
-        <v>5520</v>
+        <v>-90</v>
       </c>
       <c r="D82" s="56"/>
       <c r="G82" s="56"/>
@@ -10188,33 +10235,33 @@
       <c r="I82" s="56"/>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C83" s="56"/>
-      <c r="D83" s="56"/>
+      <c r="B83" t="s">
+        <v>194</v>
+      </c>
+      <c r="C83" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D83" s="56">
+        <v>300</v>
+      </c>
       <c r="G83" s="56"/>
       <c r="H83" s="56"/>
       <c r="I83" s="56"/>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C84" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D84" s="56">
-        <v>300</v>
-      </c>
+        <v>-12807</v>
+      </c>
+      <c r="D84" s="56"/>
       <c r="G84" s="56"/>
       <c r="H84" s="56"/>
       <c r="I84" s="56"/>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B85" t="s">
-        <v>197</v>
-      </c>
-      <c r="C85" s="56">
-        <v>-90</v>
-      </c>
+      <c r="C85" s="56"/>
       <c r="D85" s="56"/>
       <c r="G85" s="56"/>
       <c r="H85" s="56"/>
@@ -10222,10 +10269,10 @@
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C86" s="56">
-        <v>240</v>
+        <v>5520</v>
       </c>
       <c r="D86" s="56"/>
       <c r="G86" s="56"/>
@@ -10241,7 +10288,7 @@
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C88" s="56">
         <v>2000</v>
@@ -10255,10 +10302,10 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="C89" s="56">
-        <v>-50</v>
+        <v>-90</v>
       </c>
       <c r="D89" s="56"/>
       <c r="G89" s="56"/>
@@ -10267,10 +10314,10 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C90" s="56">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="D90" s="56"/>
       <c r="G90" s="56"/>
@@ -10286,7 +10333,7 @@
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="C92" s="56">
         <v>2000</v>
@@ -10300,10 +10347,10 @@
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C93" s="56">
-        <v>8000</v>
+        <v>-50</v>
       </c>
       <c r="D93" s="56"/>
       <c r="G93" s="56"/>
@@ -10312,10 +10359,10 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="C94" s="56">
-        <v>4180</v>
+        <v>300</v>
       </c>
       <c r="D94" s="56"/>
       <c r="G94" s="56"/>
@@ -10331,7 +10378,7 @@
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C96" s="56">
         <v>2000</v>
@@ -10345,28 +10392,24 @@
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C97" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D97" s="56">
-        <v>300</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="D97" s="56"/>
       <c r="G97" s="56"/>
       <c r="H97" s="56"/>
       <c r="I97" s="56"/>
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C98" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D98" s="56">
-        <v>300</v>
-      </c>
+        <v>4180</v>
+      </c>
+      <c r="D98" s="56"/>
       <c r="G98" s="56"/>
       <c r="H98" s="56"/>
       <c r="I98" s="56"/>
@@ -10380,26 +10423,35 @@
     </row>
     <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C100" s="56">
-        <v>-20000</v>
-      </c>
-      <c r="D100" s="56"/>
+        <v>2000</v>
+      </c>
+      <c r="D100" s="56">
+        <v>300</v>
+      </c>
       <c r="G100" s="56"/>
       <c r="H100" s="56"/>
       <c r="I100" s="56"/>
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C101" s="56"/>
-      <c r="D101" s="56"/>
+      <c r="B101" t="s">
+        <v>206</v>
+      </c>
+      <c r="C101" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D101" s="56">
+        <v>300</v>
+      </c>
       <c r="G101" s="56"/>
       <c r="H101" s="56"/>
       <c r="I101" s="56"/>
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C102" s="56">
         <v>2000</v>
@@ -10412,25 +10464,18 @@
       <c r="I102" s="56"/>
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
-        <v>209</v>
-      </c>
-      <c r="C103" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D103" s="56">
-        <v>300</v>
-      </c>
+      <c r="C103" s="56"/>
+      <c r="D103" s="56"/>
       <c r="G103" s="56"/>
       <c r="H103" s="56"/>
       <c r="I103" s="56"/>
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C104" s="56">
-        <v>8000</v>
+        <v>-20000</v>
       </c>
       <c r="D104" s="56"/>
       <c r="G104" s="56"/>
@@ -10438,22 +10483,15 @@
       <c r="I104" s="56"/>
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B105" t="s">
-        <v>210</v>
-      </c>
-      <c r="C105" s="56">
-        <v>2000</v>
-      </c>
-      <c r="D105" s="56">
-        <v>300</v>
-      </c>
+      <c r="C105" s="56"/>
+      <c r="D105" s="56"/>
       <c r="G105" s="56"/>
       <c r="H105" s="56"/>
       <c r="I105" s="56"/>
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C106" s="56">
         <v>2000</v>
@@ -10466,21 +10504,55 @@
       <c r="I106" s="56"/>
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B107" t="s">
+        <v>210</v>
+      </c>
+      <c r="C107" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D107" s="56">
+        <v>300</v>
+      </c>
       <c r="G107" s="56"/>
       <c r="H107" s="56"/>
       <c r="I107" s="56"/>
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>211</v>
+      </c>
+      <c r="C108" s="56">
+        <v>8000</v>
+      </c>
+      <c r="D108" s="56"/>
       <c r="G108" s="56"/>
       <c r="H108" s="56"/>
       <c r="I108" s="56"/>
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>212</v>
+      </c>
+      <c r="C109" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D109" s="56">
+        <v>300</v>
+      </c>
       <c r="G109" s="56"/>
       <c r="H109" s="56"/>
       <c r="I109" s="56"/>
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>213</v>
+      </c>
+      <c r="C110" s="56">
+        <v>2000</v>
+      </c>
+      <c r="D110" s="56">
+        <v>300</v>
+      </c>
       <c r="G110" s="56"/>
       <c r="H110" s="56"/>
       <c r="I110" s="56"/>
@@ -11685,27 +11757,19 @@
     <mergeCell ref="M3:M4"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
-  <conditionalFormatting sqref="B5:C5">
-    <cfRule type="cellIs" dxfId="11" priority="67" operator="greaterThan">
+  <conditionalFormatting sqref="B5:C5 C70:D70 C75:D110">
+    <cfRule type="cellIs" dxfId="9" priority="67" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="68" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="68" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:D52">
-    <cfRule type="cellIs" dxfId="9" priority="61" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="61" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="62" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C70:D106">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11751,13 +11815,13 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="65" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="C1" s="66" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="D1" s="65" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
@@ -11765,77 +11829,77 @@
         <v>22</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="D2" s="57"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="57" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="D3" s="57"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="57" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="D4" s="57"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="57" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="D5" s="57"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="57" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="D6" s="57"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="57" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="D7" s="57"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="57" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="D8" s="57"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="57" t="s">
-        <v>119</v>
+        <v>221</v>
       </c>
       <c r="C9" s="40"/>
       <c r="D9" s="57"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="57" t="s">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="D10" s="57"/>
     </row>
